--- a/results/Int All Data -0.9/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_4_permute.xlsx
@@ -440,1353 +440,1353 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7866306697431114</v>
+        <v>0.7880463105780102</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7872234386973582</v>
+        <v>0.7876316349846108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7855465242199966</v>
+        <v>0.7866917853605506</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7850213501893358</v>
+        <v>0.7875978375228176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7793458282374466</v>
+        <v>0.7870050685685707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7788206542067858</v>
+        <v>0.7903251000615008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7778470071209326</v>
+        <v>0.7900456143152739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7847639291072847</v>
+        <v>0.7917901237162217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7844506458992646</v>
+        <v>0.7914768405082018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7863914607648244</v>
+        <v>0.7798307255001674</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7957041499780755</v>
+        <v>0.7815076399775291</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7963125042903514</v>
+        <v>0.782066611469983</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7988278760063938</v>
+        <v>0.7814738425157359</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7976423380978999</v>
+        <v>0.7795512397539405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8023597983219648</v>
+        <v>0.7835498472284681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8023506922700827</v>
+        <v>0.7843883044671489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8030786510715021</v>
+        <v>0.7835160497666749</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8042641889799961</v>
+        <v>0.7873859467001769</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8013770451842295</v>
+        <v>0.7860990164063036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8009844342550059</v>
+        <v>0.7814153536440318</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8000536906828277</v>
+        <v>0.7828127823751665</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7983429787436731</v>
+        <v>0.780890179613371</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7970560484497997</v>
+        <v>0.7808563821515779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7956130894592546</v>
+        <v>0.7811358678978049</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7942156607281199</v>
+        <v>0.7792470625978025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7988902174385096</v>
+        <v>0.7811267618459228</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7991697031847366</v>
+        <v>0.7827789849133735</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7991697031847366</v>
+        <v>0.7833379564058274</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7971795054993549</v>
+        <v>0.7848367775223413</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7971795054993549</v>
+        <v>0.7844221019289419</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7979503678144495</v>
+        <v>0.7723430992237441</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7942494581899131</v>
+        <v>0.7729696656397842</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7944275515507606</v>
+        <v>0.77645868444168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7944275515507606</v>
+        <v>0.7796006225737626</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8001524563224719</v>
+        <v>0.7834029245836782</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7933005025139708</v>
+        <v>0.7830896413756583</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7977540623498377</v>
+        <v>0.782429277497825</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8006438328913397</v>
+        <v>0.7803714848888572</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7970781131139755</v>
+        <v>0.7818027110817849</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7923515468380286</v>
+        <v>0.7744346892945051</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7911998063913277</v>
+        <v>0.7750612557105452</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7934110009512322</v>
+        <v>0.7732738427959222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7952724880955884</v>
+        <v>0.7732062478723359</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7970078914446541</v>
+        <v>0.7706661847463825</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7963137301050278</v>
+        <v>0.7671862719963688</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7973549721144673</v>
+        <v>0.7696925376605293</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7906291021012565</v>
+        <v>0.7705985898227963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7885530973885244</v>
+        <v>0.7709118730308163</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7885530973885244</v>
+        <v>0.7755032494595908</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7879941258960705</v>
+        <v>0.7748766830435507</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7857218157187267</v>
+        <v>0.7609999355571713</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7776752179498494</v>
+        <v>0.7599495874958497</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7765234775031487</v>
+        <v>0.7621516760038722</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7944807869309943</v>
+        <v>0.7530079740995865</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7925828755791098</v>
+        <v>0.7654717074968024</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7645978767488872</v>
+        <v>0.7626950621382971</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7673407246455994</v>
+        <v>0.7639143975085843</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7670612388993725</v>
+        <v>0.7519420406802361</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7539930037502924</v>
+        <v>0.7482840345693749</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.76419230720737</v>
+        <v>0.7482840345693749</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7664619906389787</v>
+        <v>0.6144159658509045</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7644406222375391</v>
+        <v>0.6273619697651059</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7236330765426703</v>
+        <v>0.6289283858052062</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7288081158738098</v>
+        <v>0.6311213682613466</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7146895326634082</v>
+        <v>0.622595126721219</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7134584644955038</v>
+        <v>0.6229760048528252</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7130099914403112</v>
+        <v>0.6229760048528252</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7266801015955204</v>
+        <v>0.6367513599538254</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.730797087744515</v>
+        <v>0.6367513599538254</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6896359820736861</v>
+        <v>0.6301139237137001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6929833317222626</v>
+        <v>0.6298006405056801</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6894267179967807</v>
+        <v>0.6326539868396537</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6760881031533557</v>
+        <v>0.6314008540075735</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6780691947868553</v>
+        <v>0.6296225471448325</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6750624465019452</v>
+        <v>0.6300034252764387</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6753419322481722</v>
+        <v>0.6184119465796969</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6733855320245835</v>
+        <v>0.6168364244877145</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6747491632939251</v>
+        <v>0.6162436555334675</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6881242023448784</v>
+        <v>0.6152700084476143</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6709221698740984</v>
+        <v>0.593383087399886</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6748869798868329</v>
+        <v>0.5899031746498723</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6837473434844799</v>
+        <v>0.5899031746498723</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6817818372090091</v>
+        <v>0.5932296854489494</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.679681141086366</v>
+        <v>0.5929164022409293</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.679681141086366</v>
+        <v>0.583864986670141</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6948409663062072</v>
+        <v>0.5841691638262789</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6915391469170411</v>
+        <v>0.5763032861639846</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6823824864004617</v>
+        <v>0.5846696464470287</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.68631997825755</v>
+        <v>0.5961935302201843</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6847873596792429</v>
+        <v>0.5993601597621779</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6847873596792429</v>
+        <v>0.6044402860140849</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.674645319279193</v>
+        <v>0.6202214241584958</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6881126446636434</v>
+        <v>0.6139648660499768</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5967549533419911</v>
+        <v>0.6252833383066386</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.576528135598919</v>
+        <v>0.6039060059315421</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5825416321687393</v>
+        <v>0.5678199481375322</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.578290857103631</v>
+        <v>0.5423088184407356</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.578290857103631</v>
+        <v>0.5287024506487011</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5839546462579029</v>
+        <v>0.5310735264656891</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5934545348838838</v>
+        <v>0.5310735264656891</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5708890378545581</v>
+        <v>0.5308434235392842</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.566343191685194</v>
+        <v>0.5308434235392842</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5669112692295299</v>
+        <v>0.5286166436213507</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.575935366644672</v>
+        <v>0.5286166436213507</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.575935366644672</v>
+        <v>0.5306068413067324</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5372507568530045</v>
+        <v>0.5311996102609795</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.512925165064702</v>
+        <v>0.5287947369821984</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5039933539830571</v>
+        <v>0.5243073796845383</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5039933539830571</v>
+        <v>0.5201086141849873</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4975860206693368</v>
+        <v>0.518821683891114</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4972727374613168</v>
+        <v>0.518821683891114</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4972727374613168</v>
+        <v>0.5172123643373385</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4983906804462245</v>
+        <v>0.5172123643373385</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4983906804462245</v>
+        <v>0.5172123643373385</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4983906804462245</v>
+        <v>0.514334326593454</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4983906804462245</v>
+        <v>0.5112352919750466</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5000675949235862</v>
+        <v>0.5112352919750466</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5</v>
+        <v>0.5109220087670265</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5</v>
+        <v>0.5103539312226906</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5</v>
+        <v>0.510489121069863</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5</v>
+        <v>0.5034708066981316</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.5018796992481203</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.5013207277556664</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.5026076580495398</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5</v>
+        <v>0.5026076580495398</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5</v>
+        <v>0.5045211547594531</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5</v>
+        <v>0.5045211547594531</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.503268021927373</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.5006603638778332</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.5006603638778332</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.5003470806698131</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1796,7 +1796,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -1806,17 +1806,17 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -1826,7 +1826,7 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1836,7 +1836,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1846,27 +1846,27 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,77 +1886,77 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
